--- a/data/12April-Tigers-v-89ers.xlsx
+++ b/data/12April-Tigers-v-89ers.xlsx
@@ -289,7 +289,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:O149"/>
   <sheetData>
     <row r="1">
@@ -360,8 +360,10 @@
       <c r="D3" t="s">
         <v>16</v>
       </c>
-      <c r="E3" t="s">
-        <v>17</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
       </c>
       <c r="J3" t="s">
         <v>18</v>
@@ -439,8 +441,10 @@
       <c r="D11" t="s">
         <v>16</v>
       </c>
-      <c r="E11" t="s">
-        <v>21</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>DCLM</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -472,8 +476,10 @@
       <c r="D14" t="s">
         <v>16</v>
       </c>
-      <c r="E14" t="s">
-        <v>22</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>DCLC</t>
+        </is>
       </c>
       <c r="L14" t="s">
         <v>23</v>
@@ -811,8 +817,10 @@
       <c r="D47" t="s">
         <v>40</v>
       </c>
-      <c r="E47" t="s">
-        <v>41</v>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>DM</t>
+        </is>
       </c>
       <c r="I47" t="s">
         <v>32</v>
@@ -902,8 +910,10 @@
       <c r="D55" t="s">
         <v>16</v>
       </c>
-      <c r="E55" t="s">
-        <v>44</v>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>DCUC</t>
+        </is>
       </c>
       <c r="I55" t="s">
         <v>32</v>
@@ -1002,8 +1012,10 @@
       <c r="D63" t="s">
         <v>40</v>
       </c>
-      <c r="E63" t="s">
-        <v>41</v>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>DM</t>
+        </is>
       </c>
       <c r="I63" t="s">
         <v>32</v>
@@ -1111,8 +1123,10 @@
       <c r="D71" t="s">
         <v>16</v>
       </c>
-      <c r="E71" t="s">
-        <v>55</v>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>UCDC</t>
+        </is>
       </c>
       <c r="I71" t="s">
         <v>32</v>
@@ -1241,8 +1255,10 @@
       <c r="D85" t="s">
         <v>16</v>
       </c>
-      <c r="E85" t="s">
-        <v>58</v>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>DCRN</t>
+        </is>
       </c>
       <c r="I85" t="s">
         <v>28</v>
@@ -1329,8 +1345,10 @@
       <c r="D93" t="s">
         <v>40</v>
       </c>
-      <c r="E93" t="s">
-        <v>41</v>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>DM</t>
+        </is>
       </c>
       <c r="I93" t="s">
         <v>37</v>
@@ -1573,8 +1591,10 @@
       <c r="D110" t="s">
         <v>16</v>
       </c>
-      <c r="E110" t="s">
-        <v>78</v>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>RCDN</t>
+        </is>
       </c>
       <c r="I110" t="s">
         <v>32</v>
@@ -1811,8 +1831,10 @@
       <c r="D133" t="s">
         <v>16</v>
       </c>
-      <c r="E133" t="s">
-        <v>17</v>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
       </c>
       <c r="I133" t="s">
         <v>37</v>
